--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Person.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Person.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O guia</t>
+          <t>A guia</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huge Shadow </t>
+          <t xml:space="preserve">Sombra Enorme </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O Senhor de Mysilia</t>
+          <t>O Lorde de Mysilia</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Admiradores de Melvin</t>
+          <t>Fã de Melvin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Admiradores de Melvin</t>
+          <t>Fã de Melvin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Impuro</t>
+          <t>Inpure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -1596,6 +1596,60 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>不浄なるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EA 23.333</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pebble</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EA 23.333</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Seixo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pebble</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>石ころ</t>
         </is>
       </c>
     </row>
